--- a/b1/AC02/root_finding.xlsx
+++ b/b1/AC02/root_finding.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Problema" sheetId="1" state="visible" r:id="rId3"/>
@@ -167,7 +167,7 @@
     <numFmt numFmtId="171" formatCode="#,##0.00"/>
     <numFmt numFmtId="172" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,12 +230,6 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -291,7 +285,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -352,7 +346,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -361,10 +355,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -480,10 +470,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.130276008492569"/>
-          <c:y val="0.0498263626755247"/>
-          <c:w val="0.674904458598726"/>
-          <c:h val="0.90653782273894"/>
+          <c:x val="0.130298139811433"/>
+          <c:y val="0.0498414136837336"/>
+          <c:w val="0.674849231291939"/>
+          <c:h val="0.906207521522429"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -632,11 +622,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="17442720"/>
-        <c:axId val="88151251"/>
+        <c:axId val="47826101"/>
+        <c:axId val="13006912"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="17442720"/>
+        <c:axId val="47826101"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -667,12 +657,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88151251"/>
+        <c:crossAx val="13006912"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="88151251"/>
+        <c:axId val="13006912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -712,7 +702,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17442720"/>
+        <c:crossAx val="47826101"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -775,10 +765,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.130276008492569"/>
-          <c:y val="0.0498263626755247"/>
-          <c:w val="0.674904458598726"/>
-          <c:h val="0.90653782273894"/>
+          <c:x val="0.130298139811433"/>
+          <c:y val="0.0498414136837336"/>
+          <c:w val="0.674849231291939"/>
+          <c:h val="0.906207521522429"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -957,11 +947,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="16477746"/>
-        <c:axId val="37526924"/>
+        <c:axId val="20423033"/>
+        <c:axId val="39723610"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="16477746"/>
+        <c:axId val="20423033"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -992,12 +982,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37526924"/>
+        <c:crossAx val="39723610"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="37526924"/>
+        <c:axId val="39723610"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1037,7 +1027,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16477746"/>
+        <c:crossAx val="20423033"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1272,11 +1262,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="31611075"/>
-        <c:axId val="29199486"/>
+        <c:axId val="80898423"/>
+        <c:axId val="32368587"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="31611075"/>
+        <c:axId val="80898423"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1307,12 +1297,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29199486"/>
+        <c:crossAx val="32368587"/>
         <c:crossesAt val="0"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="29199486"/>
+        <c:axId val="32368587"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1352,7 +1342,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31611075"/>
+        <c:crossAx val="80898423"/>
         <c:crossesAt val="0"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1390,9 +1380,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>809280</xdr:colOff>
+      <xdr:colOff>808560</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>117000</xdr:rowOff>
+      <xdr:rowOff>116280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1401,7 +1391,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="3282480" y="3886200"/>
-        <a:ext cx="4238640" cy="2383920"/>
+        <a:ext cx="4237920" cy="2383200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1420,9 +1410,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>809280</xdr:colOff>
+      <xdr:colOff>808560</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>118800</xdr:rowOff>
+      <xdr:rowOff>118080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1431,7 +1421,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="3282480" y="487440"/>
-        <a:ext cx="4238640" cy="2383920"/>
+        <a:ext cx="4237920" cy="2383200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1455,9 +1445,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>822960</xdr:colOff>
+      <xdr:colOff>822240</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>13320</xdr:rowOff>
+      <xdr:rowOff>12600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1466,7 +1456,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6963480" y="488160"/>
-        <a:ext cx="3392280" cy="2613960"/>
+        <a:ext cx="3391560" cy="2613240"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2239,7 +2229,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="9" t="n">
-        <f aca="false">IF(H5&lt;0,G5,C5)</f>
+        <f aca="false">IF(I5&lt;0,C5,G5)</f>
         <v>0.008</v>
       </c>
       <c r="D6" s="9" t="n">
@@ -2280,7 +2270,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="9" t="n">
-        <f aca="false">IF(H6&lt;0,G6,C6)</f>
+        <f aca="false">IF(I6&lt;0,C6,G6)</f>
         <v>0.008</v>
       </c>
       <c r="D7" s="9" t="n">
@@ -2321,7 +2311,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="9" t="n">
-        <f aca="false">IF(H7&lt;0,G7,C7)</f>
+        <f aca="false">IF(I7&lt;0,C7,G7)</f>
         <v>0.008125</v>
       </c>
       <c r="D8" s="9" t="n">
@@ -2362,7 +2352,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="9" t="n">
-        <f aca="false">IF(H8&lt;0,G8,C8)</f>
+        <f aca="false">IF(I8&lt;0,C8,G8)</f>
         <v>0.008125</v>
       </c>
       <c r="D9" s="9" t="n">
@@ -2403,7 +2393,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="9" t="n">
-        <f aca="false">IF(H9&lt;0,G9,C9)</f>
+        <f aca="false">IF(I9&lt;0,C9,G9)</f>
         <v>0.00815625</v>
       </c>
       <c r="D10" s="9" t="n">
@@ -2444,7 +2434,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="9" t="n">
-        <f aca="false">IF(H10&lt;0,G10,C10)</f>
+        <f aca="false">IF(I10&lt;0,C10,G10)</f>
         <v>0.00815625</v>
       </c>
       <c r="D11" s="9" t="n">
@@ -2485,7 +2475,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="9" t="n">
-        <f aca="false">IF(H11&lt;0,G11,C11)</f>
+        <f aca="false">IF(I11&lt;0,C11,G11)</f>
         <v>0.0081640625</v>
       </c>
       <c r="D12" s="9" t="n">
@@ -2526,7 +2516,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="9" t="n">
-        <f aca="false">IF(H12&lt;0,G12,C12)</f>
+        <f aca="false">IF(I12&lt;0,C12,G12)</f>
         <v>0.0081640625</v>
       </c>
       <c r="D13" s="9" t="n">
@@ -2567,7 +2557,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="9" t="n">
-        <f aca="false">IF(H13&lt;0,G13,C13)</f>
+        <f aca="false">IF(I13&lt;0,C13,G13)</f>
         <v>0.008166015625</v>
       </c>
       <c r="D14" s="9" t="n">
@@ -2608,7 +2598,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="9" t="n">
-        <f aca="false">IF(H14&lt;0,G14,C14)</f>
+        <f aca="false">IF(I14&lt;0,C14,G14)</f>
         <v>0.008166015625</v>
       </c>
       <c r="D15" s="9" t="n">
@@ -2649,7 +2639,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="9" t="n">
-        <f aca="false">IF(H15&lt;0,G15,C15)</f>
+        <f aca="false">IF(I15&lt;0,C15,G15)</f>
         <v>0.00816650390625</v>
       </c>
       <c r="D16" s="9" t="n">
@@ -3218,8 +3208,8 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="4.5"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="10.7"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16382" min="8" style="18" width="10.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="18" width="10.16"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16382" min="8" style="15" width="10.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="15" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3503,7 +3493,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="2" style="1" width="10.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="7.66"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="10.7"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="22" min="10" style="18" width="10.7"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="22" min="10" style="15" width="10.7"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16374" min="23" style="1" width="10.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16375" style="1" width="10.16"/>
   </cols>
@@ -3534,109 +3524,109 @@
       <c r="I4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="19" t="n">
+      <c r="B5" s="18" t="n">
         <v>0.001</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="18" t="n">
         <f aca="false">T_air  +  (q / (2*PI())) * ((1/k)*LN((r_w+B5)/r_w) + (1/h) * (1/(r_w+B5)))</f>
         <v>445.926381882158</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="18" t="n">
         <f aca="false">B5^2</f>
         <v>1E-006</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="18" t="n">
         <f aca="false">B5</f>
         <v>0.001</v>
       </c>
-      <c r="F5" s="20" t="n">
+      <c r="F5" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="20" t="n">
+      <c r="H5" s="19" t="n">
         <f aca="false" t="array" ref="H5:H7">MMULT(MINVERSE(D5:F7),C5:C7)</f>
         <v>510486.895203445</v>
       </c>
       <c r="I5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="19" t="n">
+      <c r="B6" s="18" t="n">
         <v>0.005</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="18" t="n">
         <f aca="false">T_air  +  (q / (2*PI())) * ((1/k)*LN((r_w+B6)/r_w) + (1/h) * (1/(r_w+B6)))</f>
         <v>425.989022581162</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="18" t="n">
         <f aca="false">B6^2</f>
         <v>2.5E-005</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="18" t="n">
         <f aca="false">B6</f>
         <v>0.005</v>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="20" t="n">
+      <c r="H6" s="19" t="n">
         <v>-8047.26119646965</v>
       </c>
       <c r="I6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="18" t="n">
         <v>0.01</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="18" t="n">
         <f aca="false">T_air  +  (q / (2*PI())) * ((1/k)*LN((r_w+B7)/r_w) + (1/h) * (1/(r_w+B7)))</f>
         <v>424.039233739072</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="18" t="n">
         <f aca="false">B7^2</f>
         <v>0.0001</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="18" t="n">
         <f aca="false">B7</f>
         <v>0.01</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="20" t="n">
+      <c r="H7" s="19" t="n">
         <v>453.463156183424</v>
       </c>
       <c r="I7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="19" t="n">
+      <c r="B8" s="18" t="n">
         <f aca="false">-$H$6/(2*$H$5)</f>
-        <v>0.00788194689431029</v>
-      </c>
-      <c r="C8" s="19" t="n">
+        <v>0.00788194689431015</v>
+      </c>
+      <c r="C8" s="18" t="n">
         <f aca="false">T_air  +  (q / (2*PI())) * ((1/k)*LN((r_w+B8)/r_w) + (1/h) * (1/(r_w+B8)))</f>
         <v>423.554318880432</v>
       </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
       <c r="I8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="23" t="n">
+      <c r="B9" s="22" t="n">
         <f aca="false">B6-0.5*(((B6-B5)^2*(C6-C7)-(B6-B7)^2*(C6-C5)) / ((B6-B5)*(C6-C7)-(B6-B7)*(C6-C5)))</f>
         <v>0.00788194689431029</v>
       </c>
-      <c r="C9" s="22"/>
+      <c r="C9" s="21"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
@@ -3645,8 +3635,8 @@
       <c r="I9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
@@ -3677,30 +3667,30 @@
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="16" t="n">
         <f aca="false">$B$8</f>
-        <v>0.00788194689431029</v>
+        <v>0.00788194689431015</v>
       </c>
       <c r="C12" s="16" t="n">
         <f aca="false">$C$8</f>
         <v>423.554318880432</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="18" t="n">
         <f aca="false">B12^2</f>
-        <v>6.21250868447276E-005</v>
-      </c>
-      <c r="E12" s="20" t="n">
+        <v>6.21250868447254E-005</v>
+      </c>
+      <c r="E12" s="19" t="n">
         <f aca="false">B12</f>
-        <v>0.00788194689431029</v>
-      </c>
-      <c r="F12" s="20" t="n">
+        <v>0.00788194689431015</v>
+      </c>
+      <c r="F12" s="19" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="20" t="n">
+      <c r="H12" s="19" t="n">
         <f aca="false" t="array" ref="H12:H14">MMULT(MINVERSE(D12:F14),C12:C14)</f>
-        <v>214751.161139973</v>
+        <v>214751.161139987</v>
       </c>
       <c r="I12" s="16"/>
     </row>
@@ -3712,23 +3702,23 @@
         <f aca="false">T_air  +  (q / (2*PI())) * ((1/k)*LN((r_w+B13)/r_w) + (1/h) * (1/(r_w+B13)))</f>
         <v>424.039233739072</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="18" t="n">
         <f aca="false">B13^2</f>
         <v>0.0001</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="19" t="n">
         <f aca="false">B13</f>
         <v>0.01</v>
       </c>
-      <c r="F13" s="20" t="n">
+      <c r="F13" s="19" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
-      <c r="G13" s="21" t="s">
+      <c r="G13" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H13" s="20" t="n">
-        <v>-3611.22518551763</v>
+      <c r="H13" s="19" t="n">
+        <v>-3611.22518551786</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3739,22 +3729,22 @@
         <f aca="false">T_air  +  (q / (2*PI())) * ((1/k)*LN((r_w+B14)/r_w) + (1/h) * (1/(r_w+B14)))</f>
         <v>425.989022581162</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="18" t="n">
         <f aca="false">B14^2</f>
         <v>2.5E-005</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="19" t="n">
         <f aca="false">B14</f>
         <v>0.005</v>
       </c>
-      <c r="F14" s="20" t="n">
+      <c r="F14" s="19" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
-      <c r="G14" s="21" t="s">
+      <c r="G14" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H14" s="20" t="n">
+      <c r="H14" s="19" t="n">
         <v>438.676369480251</v>
       </c>
       <c r="I14" s="16"/>
@@ -3762,17 +3752,17 @@
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="16" t="n">
         <f aca="false">-H13/(2*H12)</f>
-        <v>0.00840792935960826</v>
+        <v>0.00840792935960906</v>
       </c>
       <c r="C15" s="16" t="n">
         <f aca="false">T_air  +  (q / (2*PI())) * ((1/k)*LN((r_w+B15)/r_w) + (1/h) * (1/(r_w+B15)))</f>
         <v>423.549704716554</v>
       </c>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
       <c r="I15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3816,59 +3806,59 @@
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="16" t="n">
         <f aca="false">$B$15</f>
-        <v>0.00840792935960826</v>
+        <v>0.00840792935960906</v>
       </c>
       <c r="C19" s="16" t="n">
         <f aca="false">$C$15</f>
         <v>423.549704716554</v>
       </c>
-      <c r="D19" s="19" t="n">
+      <c r="D19" s="18" t="n">
         <f aca="false">B19^2</f>
-        <v>7.06932761161625E-005</v>
-      </c>
-      <c r="E19" s="19" t="n">
+        <v>7.0693276116176E-005</v>
+      </c>
+      <c r="E19" s="18" t="n">
         <f aca="false">B19</f>
-        <v>0.00840792935960826</v>
-      </c>
-      <c r="F19" s="20" t="n">
+        <v>0.00840792935960906</v>
+      </c>
+      <c r="F19" s="19" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
-      <c r="G19" s="21" t="s">
+      <c r="G19" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="H19" s="20" t="n">
+      <c r="H19" s="19" t="n">
         <f aca="false" t="array" ref="H19:H21">MMULT(MINVERSE(D19:F21),C19:C21)</f>
-        <v>149312.55847533</v>
+        <v>149312.558475301</v>
       </c>
       <c r="I19" s="16"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="16" t="n">
         <f aca="false">$B$8</f>
-        <v>0.00788194689431029</v>
+        <v>0.00788194689431015</v>
       </c>
       <c r="C20" s="16" t="n">
         <f aca="false">$C$8</f>
         <v>423.554318880432</v>
       </c>
-      <c r="D20" s="19" t="n">
+      <c r="D20" s="18" t="n">
         <f aca="false">B20^2</f>
-        <v>6.21250868447276E-005</v>
-      </c>
-      <c r="E20" s="19" t="n">
+        <v>6.21250868447254E-005</v>
+      </c>
+      <c r="E20" s="18" t="n">
         <f aca="false">B20</f>
-        <v>0.00788194689431029</v>
-      </c>
-      <c r="F20" s="20" t="n">
+        <v>0.00788194689431015</v>
+      </c>
+      <c r="F20" s="19" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
-      <c r="G20" s="21" t="s">
+      <c r="G20" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H20" s="20" t="n">
-        <v>-2441.05556782871</v>
+      <c r="H20" s="19" t="n">
+        <v>-2441.0555678315</v>
       </c>
       <c r="I20" s="16"/>
     </row>
@@ -3880,30 +3870,30 @@
         <f aca="false">T_air  +  (q / (2*PI())) * ((1/k)*LN((r_w+B21)/r_w) + (1/h) * (1/(r_w+B21)))</f>
         <v>424.039233739072</v>
       </c>
-      <c r="D21" s="19" t="n">
+      <c r="D21" s="18" t="n">
         <f aca="false">B21^2</f>
         <v>0.0001</v>
       </c>
-      <c r="E21" s="19" t="n">
+      <c r="E21" s="18" t="n">
         <f aca="false">B21</f>
         <v>0.01</v>
       </c>
-      <c r="F21" s="20" t="n">
+      <c r="F21" s="19" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
-      <c r="G21" s="21" t="s">
+      <c r="G21" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H21" s="20" t="n">
-        <v>433.518533569843</v>
+      <c r="H21" s="19" t="n">
+        <v>433.518533569837</v>
       </c>
       <c r="I21" s="16"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="16" t="n">
         <f aca="false">-H20/(2*H19)</f>
-        <v>0.00817431431340557</v>
+        <v>0.00817431431340338</v>
       </c>
       <c r="C22" s="16" t="n">
         <f aca="false">T_air  +  (q / (2*PI())) * ((1/k)*LN((r_w+B22)/r_w) + (1/h) * (1/(r_w+B22)))</f>
@@ -3957,28 +3947,28 @@
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="16" t="n">
         <f aca="false">$B$22</f>
-        <v>0.00817431431340557</v>
+        <v>0.00817431431340338</v>
       </c>
       <c r="C26" s="16" t="n">
         <f aca="false">T_air  +  (q / (2*PI())) * ((1/k)*LN((r_w+B26)/r_w) + (1/h) * (1/(r_w+B26)))</f>
         <v>423.53975946362</v>
       </c>
-      <c r="D26" s="19" t="n">
+      <c r="D26" s="18" t="n">
         <f aca="false">B26^2</f>
-        <v>6.68194144943472E-005</v>
-      </c>
-      <c r="E26" s="19" t="n">
+        <v>6.68194144943113E-005</v>
+      </c>
+      <c r="E26" s="18" t="n">
         <f aca="false">B26</f>
-        <v>0.00817431431340557</v>
-      </c>
-      <c r="F26" s="20" t="n">
+        <v>0.00817431431340338</v>
+      </c>
+      <c r="F26" s="19" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
-      <c r="G26" s="21" t="s">
+      <c r="G26" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="H26" s="20" t="n">
+      <c r="H26" s="19" t="n">
         <f aca="false" t="array" ref="H26:H28">MMULT(MINVERSE(D26:F28), C26:C28)</f>
         <v>175613.212985039</v>
       </c>
@@ -3986,63 +3976,63 @@
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="16" t="n">
         <f aca="false">$B$15</f>
-        <v>0.00840792935960826</v>
+        <v>0.00840792935960906</v>
       </c>
       <c r="C27" s="16" t="n">
         <f aca="false">$C$15</f>
         <v>423.549704716554</v>
       </c>
-      <c r="D27" s="19" t="n">
+      <c r="D27" s="18" t="n">
         <f aca="false">B27^2</f>
-        <v>7.06932761161625E-005</v>
-      </c>
-      <c r="E27" s="19" t="n">
+        <v>7.0693276116176E-005</v>
+      </c>
+      <c r="E27" s="18" t="n">
         <f aca="false">B27</f>
-        <v>0.00840792935960826</v>
-      </c>
-      <c r="F27" s="20" t="n">
+        <v>0.00840792935960906</v>
+      </c>
+      <c r="F27" s="19" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
-      <c r="G27" s="21" t="s">
+      <c r="G27" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H27" s="20" t="n">
-        <v>-2869.48997517675</v>
+      <c r="H27" s="19" t="n">
+        <v>-2869.48997516185</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="16" t="n">
         <f aca="false">$B$8</f>
-        <v>0.00788194689431029</v>
+        <v>0.00788194689431015</v>
       </c>
       <c r="C28" s="16" t="n">
         <f aca="false">$C$8</f>
         <v>423.554318880432</v>
       </c>
-      <c r="D28" s="19" t="n">
+      <c r="D28" s="18" t="n">
         <f aca="false">B28^2</f>
-        <v>6.21250868447276E-005</v>
-      </c>
-      <c r="E28" s="19" t="n">
+        <v>6.21250868447254E-005</v>
+      </c>
+      <c r="E28" s="18" t="n">
         <f aca="false">B28</f>
-        <v>0.00788194689431029</v>
-      </c>
-      <c r="F28" s="20" t="n">
+        <v>0.00788194689431015</v>
+      </c>
+      <c r="F28" s="19" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
-      <c r="G28" s="21" t="s">
+      <c r="G28" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H28" s="20" t="n">
+      <c r="H28" s="19" t="n">
         <v>435.261500370747</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="25" t="n">
+      <c r="B29" s="24" t="n">
         <f aca="false">-H27/(2*H26)</f>
-        <v>0.00816991479856634</v>
+        <v>0.00816991479867823</v>
       </c>
       <c r="C29" s="16"/>
     </row>
